--- a/Result/checksun_type/電池.xlsx
+++ b/Result/checksun_type/電池.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>342.9</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>349.62</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>360.64</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>349.62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>360.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>149201.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>230610.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>230610.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>233259.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>171123.7</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>171123.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>2953.759212330508</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>149201</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>149201.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>342.9</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>350.52</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>361.31</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>361.31</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>157819.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>265502.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>265502.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>255211.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>173574.24</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>173574.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>11566.7268693267</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>157819</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>157819.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>343.8</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>351.45</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>362.14</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>351.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>362.14</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>377227.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>269910.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>269910.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>270145.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>175420.74</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>175420.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>22534.51184827392</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>377227</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>377227.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>345.1</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>352.55</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>362.98</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>362.98</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>339381.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>223536.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>223536.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>241773.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>171120.36</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>171120.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>13889.97210933157</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>339381</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>339381.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>343.7</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>353.15</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>363.66</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>353.15</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>363.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>129426.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>202621.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>202621</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>225058.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>167082.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>167082.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>5099.487764080637</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>129426</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>129426.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>344.6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>354.18</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>364.53</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>354.18</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>364.53</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>323658.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>235907.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>235907.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>232199.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>166672.32</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>166672.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>14854.70699357643</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>323658</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>323658.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>347.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>355.45</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>365.36</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>355.45</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>365.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>179862.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>244919.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>244919.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>214535.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>161724.02</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>161724.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>7449.637785942701</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>179862</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>179862.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>351.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>356.62</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>366.12</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>366.12</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>145356.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>270380.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>270380.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>209544.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>160107.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>160107.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>12011.6232826823</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>145356</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>145356.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>353.7</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>357.58</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>366.89</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>357.58</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>366.89</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>234803.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>260010.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>260010.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>220986.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>160389.98</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>160389.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>21796.83030364304</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>234803</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>234803.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>355.4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>358.68</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>367.8</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>358.68</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>367.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>295860.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>247496.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>247496.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>227307.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>158869.78</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>158869.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>25413.63210845689</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>295860</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>295860.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>358.2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>359.6</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>368.71</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>359.6</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>368.71</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>368718.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>228492.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>228492</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>216922.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>157286.56</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>157286.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>23131.04068288894</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>368718</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>368718.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>125.3</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>134.32</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>141.04</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>134.32</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>141.04</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>498901.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>365940.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>365940.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>479466.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1071362.34</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1071362.34</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-139227.8162722384</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>498901</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>498901.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>124.6</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>134.72</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>141.74</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>134.72</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>141.74</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>295387.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>362617.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>362617.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>497331.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1071880.36</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1071880.36</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-155289.580176622</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>295387</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>295387.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>125.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>142.67</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>142.67</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>267896.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>603311.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>603311.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>605514.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1078057.96</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1078057.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-150883.8293194333</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>267896</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>267896.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>127.6</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>143.56</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>143.56</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>411695.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>608536.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>608536.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>744226.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1081455.44</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1081455.44</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-136255.7270477555</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>411695</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>411695.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>129.9</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>137.35</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>144.37</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>137.35</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>144.37</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>355823.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>585515.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>585515</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>819050.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1078409.64</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1078409.64</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-125899.1978365104</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>355823</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>355823.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>131.4</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>137.68</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>144.98</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>137.68</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>144.98</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>482286.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>592992.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>592992.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1019901.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1081460.4</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1081460.4</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-100621.4704691418</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>482286</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>482286.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>133.2</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>145.37</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>145.37</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1498856.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>632046.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>632046.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1131680.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1075319.16</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1075319.16</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-74466.41457043169</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1498856</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1498856.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>135.4</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>137.07</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>145.78</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>137.07</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>145.78</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>294021.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>607717.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>607717.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1232806.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1049475.74</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1049475.74</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-143360.7484804732</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>294021</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>294021.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>138.9</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>136.72</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>146.2</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>136.72</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>146.2</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>296589.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>879917.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>879917.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1270495.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1053609.7</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1053609.7</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-107571.7344776583</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>296589</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>296589.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>142.3</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>146.78</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>146.78</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>393212.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1052585.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1052585.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1282174.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1065844.62</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1065844.62</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-52877.8668137209</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>393212</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>393212.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>143.7</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>135.82</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>147.38</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>135.82</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>147.38</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>677553.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1446810.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1446810.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1297394.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1114847.44</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1114847.44</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>16792.26080667996</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>677553</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>677553.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>217717</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>149413</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>216732</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>221658</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>301588</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>199194</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>216632</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>357016</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>609988</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>600689</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>797538</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>321219</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>681031</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>19.51</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>25.55</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>14679.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>13457.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>13457.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>24804.8</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>79987.74</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>79987.74000000001</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-12447.46825365585</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>14679</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>14679.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>19.59</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>25.63</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>9083.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>13991.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>13991.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>24803.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>81528.18</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>81528.17999999999</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-13471.99349462583</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>9083</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>9083.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>19.83</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>23.53</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>25.75</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>25.75</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>11481.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>20724.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>20724.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>25722.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>83537.94</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>83537.94</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-13854.88692834631</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>11481</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>11481.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>20.12</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>25.84</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>13356.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>23124.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>23124.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>28107.4</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>83806.82</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>83806.82000000001</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-14163.98872907747</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>13356</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>13356.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>20.41</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>25.92</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>25.92</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>18688.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>28676.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>28676.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>32944.4</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>84332.14</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>84332.14</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-14300.59884694067</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>18688</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>18688.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>20.81</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>25.65</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>25.99</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>25.99</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>17351.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>36152.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>36152.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>33280.1</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>85105.66</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>85105.66</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-14556.3061993545</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>17351</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>17351.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>21.5</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>26.14</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>26.04</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>26.04</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>42747.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>35615.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>35615.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>34602.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>85690.7</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>85690.7</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-14258.48433854015</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>42747</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>42747.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>22.0</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>26.57</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>26.08</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>26.08</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>23482.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>30720.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>30720</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>36165.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>85235.06</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>85235.06</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-16044.79295385752</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>23482</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>23482.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>22.44</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>27.04</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>26.13</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>26.13</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>41115.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>33090.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>33090</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>49446.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>85489.62</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>85489.62</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-15959.52694167313</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>41115</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>41115.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>22.98</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>26.19</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>26.19</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>56066.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>37212.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>37212.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>50980.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>85603.6</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>85603.60000000001</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-17156.98524777853</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>56066</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>56066.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>23.51</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>27.88</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>26.22</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>26.22</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>14667.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>30408.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>30408</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>55698.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>85293.6</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>85293.60000000001</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-19856.78335479416</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>14667</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>14667.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>35.92999999999999</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>43.47</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>43.47</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>69420.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>64496.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>64496.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>80504.4</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>285477.32</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>285477.32</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-31595.69257733077</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>69420</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>69420.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>35.73</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>43.86</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>43.86</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>63706.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>64473.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>64473.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>80582.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>340787.1</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>340787.1</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-34337.52392579356</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>63706</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>63706.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>35.86</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>38.99</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>44.16</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>44.16</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>53769.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>95884.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>95884.39999999999</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>83542.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>376130.54</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>376130.54</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-36415.87142624777</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>53769</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>53769.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>36.17</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>39.44</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>44.39</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>44.39</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>72934.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>97826.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>97826</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>95043.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>419286.5</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>419286.5</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-37019.69387595924</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>72934</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>72934.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>36.86</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>39.99</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>44.58</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>44.58</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>62652.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>95677.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>95677.60000000001</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>97483.7</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>448385.62</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>448385.62</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-38613.5583085485</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>62652</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>62652.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>37.28</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>40.34</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>44.69</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>44.69</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>69307.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>96512.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>96512.60000000001</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>117272.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>465981.56</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>465981.56</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-38409.80898694211</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>69307</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>69307.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>37.95</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>40.53</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>44.74</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>44.74</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>220760.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>96690.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>96690.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>142581.5</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>471779.24</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>471779.24</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-37459.99534939937</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>220760</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>220760.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>38.32</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>40.64</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>44.74</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>44.74</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>63477.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>71201.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>71201</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>169046.9</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>468357.3</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>468357.3</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-50992.36889043119</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>63477</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>63477.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>38.6</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>40.79</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>44.74</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>44.74</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>62192.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>92261.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>92261.39999999999</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>174766.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>469555.86</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>469555.86</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-51651.42506010411</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>62192</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>62192.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>39.11</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>40.96</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>44.74</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>44.74</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>66827.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>99289.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>99289.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>180739.9</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>471238.38</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>471238.38</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-50610.56155034743</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>66827</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>66827.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>39.66</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>44.75</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>44.75</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>70198.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>138032.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>138032</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>188503.3</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>472614.5</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>472614.5</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-47812.70076675402</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>70198</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>70198.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>262.4</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>279.58</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>320.23</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>279.58</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>320.23</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>610412.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>623844.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>623844.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>781783.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1796574.58</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1796574.58</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-198049.6851981157</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>610412</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>610412.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>261.9</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>282.27</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>322.91</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>282.27</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>322.91</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>426146.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>691071.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>691071.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>806839.8</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1866091.2</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1866091.2</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-208115.0499583387</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>426146</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>426146.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>262.2</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>285.68</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>325.64</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>285.68</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>325.64</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>556393.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1047873.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1047873.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>842905.6</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1912323.92</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1912323.92</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-195318.6764030022</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>556393</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>556393.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>264.7</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>288.82</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>328.54</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>288.82</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>328.54</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>622771.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1049494.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1049494.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>879341.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1962117.08</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1962117.08</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-184017.5114524143</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>622771</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>622771.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>266.5</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>292.0</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>331.41</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>292</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>331.41</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>903502.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1039548.0</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1039548</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>879238.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2037649.92</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2037649.92</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-168412.8646854169</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>903502</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>903502.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>268.3</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>295.9</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>334.08</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>295.9</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>334.08</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>946545.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>939721.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>939721.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>966678.0</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2123674.18</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2123674.18</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-170184.0884223699</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>946545</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>946545.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>271.8</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>299.05</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>336.15</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>299.05</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>336.15</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>2210158.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>922608.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>922608.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1076746.2</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2165873.44</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2165873.44</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-171248.1548886469</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2210158</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2210158.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>275.7</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>301.77</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>338.3</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>301.77</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>338.3</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>564495.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>637937.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>637937.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1269911.2</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2155965.7</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2155965.7</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-302039.3514515909</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>564495</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>564495.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>278.7</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>304.05</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>340.01</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>304.05</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>340.01</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>573040.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>709189.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>709189.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1350485.7</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2184111.94</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2184111.94</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-301775.7625610968</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>573040</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>573040.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>282.8</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>306.75</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>341.66</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>306.75</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>341.66</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>404371.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>718928.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>718928.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1466039.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2232954.02</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2232954.02</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-291537.0369117805</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>404371</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>404371.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>286.6</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>309.1</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>343.38</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>343.38</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>860977.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>993634.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>993634.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1641164.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2278698.32</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2278698.32</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-248426.5703801934</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>860977</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>860977.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>106.6</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>108.1</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>104.07</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>104.07</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>145057878.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>593788097.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>593788097</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>479321116.9</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>503616744.7</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>503616744.7</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-23650333.4088847</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>145057878</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>145057878.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>106.2</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>108.62</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>103.67</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>108.62</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>103.67</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>306030753.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>605831822.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>605831822</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>482925508.1</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>501097209.48</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>501097209.48</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>5871832.046692669</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>306030753</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>306030753.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>105.4</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>109.38</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>103.29</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>109.38</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>103.29</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>447077920.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>590243015.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>590243015.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>489315642.4</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>495330461.46</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>495330461.46</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>30589552.08870697</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>447077920</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>447077920.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>104.7</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>102.88</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>102.88</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1743317302.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>543466102.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>543466102.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>477660970.6</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>486875093.54</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>486875093.54</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>49695900.25270224</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1743317302</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1743317302.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>104.7</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>110.7</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>102.45</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>102.45</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>327456632.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>277726337.8</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>277726337.8</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>339379176.3</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>452457873.28</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>452457873.28</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-63666961.16490114</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>327456632</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>327456632.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>110.92</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>101.88</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>110.92</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>101.88</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>205276503.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>364854136.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>364854136.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>350023036.0</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>446229756.4</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>446229756.4</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-71640728.50558794</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>205276503</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>205276503.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>104.7</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>111.45</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>101.52</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>101.52</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>228086721.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>360019194.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>360019194.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>362921426.6</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>442363989.72</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>442363989.72</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-67382499.15279812</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>228086721</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>228086721.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>106.0</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>112.22</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>101.21</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>112.22</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>101.21</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>213193355.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>388388269.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>388388269.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>369266039.3</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>438021378.46</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>438021378.46</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-61336748.46478415</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>213193355</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>213193355.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>106.2</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>112.38</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>100.84</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>112.38</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>100.84</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>414618478.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>411855838.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>411855838.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>376770770.5</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>434045379.66</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>434045379.66</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-48913645.82245046</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>414618478</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>414618478.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>106.7</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>112.28</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>100.41</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>112.28</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>100.41</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>763095627.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>401032014.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>401032014.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>367886601.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>426235085.54</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>426235085.54</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-51000703.58974344</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>763095627</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>763095627.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>107.7</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>111.98</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>99.93</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>111.98</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>99.93000000000001</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>181101790.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>335191935.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>335191935.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>336178419.5</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>411618185.76</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>411618185.76</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-89497598.37909961</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>181101790</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>181101790.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>51.8</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>55.89</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>55.31</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>55.31</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>18666694.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>26192714.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>26192714.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>41620383.7</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>46228207.38</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>46228207.38</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-9211387.040045172</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>18666694</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>18666694.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>55.31</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>55.31</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>13540908.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>40660637.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>40660637</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>43253617.1</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>46687023.76</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>46687023.76</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-8515030.880824275</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>13540908</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>13540908.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>52.6</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>56.64</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>55.37</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>55.37</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>12652398.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>61592727.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>61592727.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>45570354.7</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>47044971.66</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>47044971.66</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-6666936.764764994</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>12652398</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>12652398.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>53.23999999999999</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>56.95</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>55.45</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>55.45</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>38380653.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>63605316.8</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>63605316.8</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>49310688.3</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>48162302.84</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>48162302.84</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-3693499.928795837</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>38380653</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>38380653.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>54.04</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>57.22</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>55.58</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>55.58</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>47722918.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>61312748.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>61312748</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>53497718.2</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>48074409.08</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>48074409.08</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-2070421.058525763</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>47722918</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>47722918.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>54.67999999999999</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>57.42</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>55.66</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>55.66</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>91006308.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>57048053.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>57048053.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>58753272.6</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>47402419.1</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>47402419.1</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-678750.3131925911</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>91006308</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>91006308.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>55.28000000000001</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>55.72</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>55.72</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>118201361.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>45846597.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>45846597.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>55387869.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>46027316.8</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>46027316.8</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-3303914.237245455</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>118201361</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>118201361.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>55.3</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>55.72</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>55.72</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>22715344.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>29547981.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>29547981.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>49431326.0</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>44030725.78</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>44030725.78</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-9849907.155990794</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>22715344</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>22715344.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>55.9</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>55.73</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>55.73</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>26917809.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>35016059.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>35016059.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>54952369.1</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>44081171.48</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>44081171.48</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-8618898.534341604</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>26917809</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>26917809.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>56.98</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>55.73</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>55.73</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>26399444.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>45682688.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>45682688.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>69086539.7</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>44211146.0</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>44211146</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-7002761.091473415</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>26399444</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>26399444.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>58.04000000000001</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>55.75</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>55.75</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>34999028.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>60458492.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>60458492</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>84833661.9</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>44026240.04</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>44026240.04</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-4388355.598394811</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>34999028</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>34999028.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
